--- a/xls_files/Presentations.xlsx
+++ b/xls_files/Presentations.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bouch\OneDrive\Documents\pour portable\CARA website\xls_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0a8ef36ec375223/Documents/pour portable/CARA website/xls_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74388510-86AD-4665-9702-0A277BD7EAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{74388510-86AD-4665-9702-0A277BD7EAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBACC9FD-1081-42E3-BFBD-1CD333F082FC}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="210">
   <si>
     <t>Presentateur</t>
   </si>
@@ -632,6 +632,24 @@
   </si>
   <si>
     <t>8th Workshop on Insurance Mathematics (WIM)</t>
+  </si>
+  <si>
+    <t>Modélisation de l’exposition au risque en assurance automobile</t>
+  </si>
+  <si>
+    <t>Journée ModElle</t>
+  </si>
+  <si>
+    <t>ASTIN Webinar</t>
+  </si>
+  <si>
+    <t>Risk Exposure Modeling in Pay-as-You-Drive Insurance: Mileage, Duration, and Pricing Consistency</t>
+  </si>
+  <si>
+    <t>Congrès annuel de la Société Canadienne de Mathématiques Appliquées et Industrielles</t>
+  </si>
+  <si>
+    <t>Université de Régina</t>
   </si>
 </sst>
 </file>
@@ -1483,7 +1501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L98"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="20.23046875" bestFit="1" customWidth="1"/>
@@ -4334,6 +4352,78 @@
         <v>25</v>
       </c>
     </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A96" t="s">
+        <v>121</v>
+      </c>
+      <c r="D96" t="s">
+        <v>204</v>
+      </c>
+      <c r="E96" t="s">
+        <v>205</v>
+      </c>
+      <c r="F96" s="1">
+        <v>46136</v>
+      </c>
+      <c r="G96" s="1">
+        <v>46136</v>
+      </c>
+      <c r="H96" t="s">
+        <v>148</v>
+      </c>
+      <c r="I96" t="s">
+        <v>30</v>
+      </c>
+      <c r="J96" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A97" t="s">
+        <v>121</v>
+      </c>
+      <c r="D97" t="s">
+        <v>179</v>
+      </c>
+      <c r="E97" t="s">
+        <v>206</v>
+      </c>
+      <c r="F97" s="1">
+        <v>46232</v>
+      </c>
+      <c r="G97" s="1">
+        <v>46232</v>
+      </c>
+      <c r="H97" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A98" t="s">
+        <v>121</v>
+      </c>
+      <c r="D98" t="s">
+        <v>207</v>
+      </c>
+      <c r="E98" t="s">
+        <v>208</v>
+      </c>
+      <c r="F98" s="1">
+        <v>46189</v>
+      </c>
+      <c r="G98" s="1">
+        <v>46189</v>
+      </c>
+      <c r="H98" t="s">
+        <v>209</v>
+      </c>
+      <c r="I98" t="s">
+        <v>30</v>
+      </c>
+      <c r="J98" t="s">
+        <v>184</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
